--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/98.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/98.xlsx
@@ -426,13 +426,13 @@
         <v>-25.36146993705603</v>
       </c>
       <c r="E2">
-        <v>-23.5590897684188</v>
+        <v>-12.05210694798837</v>
       </c>
       <c r="F2">
-        <v>-5.236782306306853</v>
+        <v>-2.380178026937828</v>
       </c>
       <c r="G2">
-        <v>-16.43754241561896</v>
+        <v>-10.70956878271641</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-24.99358694019392</v>
       </c>
       <c r="E3">
-        <v>-24.18889104013845</v>
+        <v>-12.91578385583177</v>
       </c>
       <c r="F3">
-        <v>-5.093269310506645</v>
+        <v>-2.358053161976456</v>
       </c>
       <c r="G3">
-        <v>-14.62796354404209</v>
+        <v>-10.13671920453433</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-24.54229201525392</v>
       </c>
       <c r="E4">
-        <v>-24.93674734376635</v>
+        <v>-12.77224887244569</v>
       </c>
       <c r="F4">
-        <v>-5.237811966988533</v>
+        <v>-2.240948518977496</v>
       </c>
       <c r="G4">
-        <v>-14.63834255916406</v>
+        <v>-9.761013477288699</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-24.05978714342532</v>
       </c>
       <c r="E5">
-        <v>-25.3611681622619</v>
+        <v>-13.61635169531517</v>
       </c>
       <c r="F5">
-        <v>-4.989426001259101</v>
+        <v>-2.60380326263018</v>
       </c>
       <c r="G5">
-        <v>-14.82818154673456</v>
+        <v>-9.933382667427772</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-23.53313884699756</v>
       </c>
       <c r="E6">
-        <v>-27.0616423942544</v>
+        <v>-14.56122388455896</v>
       </c>
       <c r="F6">
-        <v>-4.772527937244885</v>
+        <v>-2.604245610823275</v>
       </c>
       <c r="G6">
-        <v>-14.86283395969241</v>
+        <v>-9.585085842271939</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-22.97913751034974</v>
       </c>
       <c r="E7">
-        <v>-24.9990828925407</v>
+        <v>-15.27513599202904</v>
       </c>
       <c r="F7">
-        <v>-4.622752483879511</v>
+        <v>-2.187826974170769</v>
       </c>
       <c r="G7">
-        <v>-14.63462355349402</v>
+        <v>-9.08364926626288</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-22.40357995010236</v>
       </c>
       <c r="E8">
-        <v>-26.44522692263467</v>
+        <v>-15.99832637359878</v>
       </c>
       <c r="F8">
-        <v>-4.979020878312537</v>
+        <v>-1.943143810731851</v>
       </c>
       <c r="G8">
-        <v>-14.49033944829385</v>
+        <v>-8.590071031473071</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-21.81178531271464</v>
       </c>
       <c r="E9">
-        <v>-25.82874915284507</v>
+        <v>-16.79480432220645</v>
       </c>
       <c r="F9">
-        <v>-4.111045088148173</v>
+        <v>-2.14622719156958</v>
       </c>
       <c r="G9">
-        <v>-14.43874199756738</v>
+        <v>-7.66787902492642</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-21.2234176726822</v>
       </c>
       <c r="E10">
-        <v>-26.6384343134657</v>
+        <v>-18.06206538732873</v>
       </c>
       <c r="F10">
-        <v>-4.726882408248423</v>
+        <v>-1.728473226663762</v>
       </c>
       <c r="G10">
-        <v>-13.74301641983226</v>
+        <v>-8.012249290217218</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-20.64673672492861</v>
       </c>
       <c r="E11">
-        <v>-27.74648202245068</v>
+        <v>-17.98683827060211</v>
       </c>
       <c r="F11">
-        <v>-4.624709916052327</v>
+        <v>-1.687855887802294</v>
       </c>
       <c r="G11">
-        <v>-13.1765958002058</v>
+        <v>-7.180391657267679</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-20.1107358006806</v>
       </c>
       <c r="E12">
-        <v>-27.05203186324875</v>
+        <v>-18.9972481345517</v>
       </c>
       <c r="F12">
-        <v>-4.977642474954278</v>
+        <v>-1.343927682568772</v>
       </c>
       <c r="G12">
-        <v>-13.92826702378388</v>
+        <v>-6.340272323059561</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-19.62246542392457</v>
       </c>
       <c r="E13">
-        <v>-28.14384259255931</v>
+        <v>-19.41534361219954</v>
       </c>
       <c r="F13">
-        <v>-4.553522506557945</v>
+        <v>-1.555147288036799</v>
       </c>
       <c r="G13">
-        <v>-12.25327986811267</v>
+        <v>-5.951461963338833</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-19.19568735706536</v>
       </c>
       <c r="E14">
-        <v>-30.25310080240939</v>
+        <v>-21.09048325511059</v>
       </c>
       <c r="F14">
-        <v>-4.279930149128727</v>
+        <v>-1.131295710678973</v>
       </c>
       <c r="G14">
-        <v>-13.31552787899419</v>
+        <v>-5.765754479083762</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-18.82919657765122</v>
       </c>
       <c r="E15">
-        <v>-31.64247666350994</v>
+        <v>-21.86772352886165</v>
       </c>
       <c r="F15">
-        <v>-3.813820237084488</v>
+        <v>-0.9397216665357397</v>
       </c>
       <c r="G15">
-        <v>-12.32914157906895</v>
+        <v>-5.86637518636986</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-18.50451934655736</v>
       </c>
       <c r="E16">
-        <v>-31.08000517718275</v>
+        <v>-22.23210967765681</v>
       </c>
       <c r="F16">
-        <v>-3.976781642767623</v>
+        <v>-0.5651952261776104</v>
       </c>
       <c r="G16">
-        <v>-11.9612537265014</v>
+        <v>-4.817122156690612</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-18.21387761069576</v>
       </c>
       <c r="E17">
-        <v>-31.85098033165031</v>
+        <v>-23.66790805834063</v>
       </c>
       <c r="F17">
-        <v>-4.032435506724708</v>
+        <v>-0.5359132668560507</v>
       </c>
       <c r="G17">
-        <v>-12.52436392198633</v>
+        <v>-4.998777765340274</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-17.93588747847325</v>
       </c>
       <c r="E18">
-        <v>-32.11891230063765</v>
+        <v>-23.54829557218557</v>
       </c>
       <c r="F18">
-        <v>-4.241979324936871</v>
+        <v>-0.3662329731688084</v>
       </c>
       <c r="G18">
-        <v>-11.75492527609342</v>
+        <v>-5.069758689283463</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-17.67157036214634</v>
       </c>
       <c r="E19">
-        <v>-32.61890702900544</v>
+        <v>-24.86806568808766</v>
       </c>
       <c r="F19">
-        <v>-4.018857736625421</v>
+        <v>0.01067502347236948</v>
       </c>
       <c r="G19">
-        <v>-11.40088350746485</v>
+        <v>-4.810402100113087</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-17.41037598840611</v>
       </c>
       <c r="E20">
-        <v>-32.96665333662767</v>
+        <v>-25.77331624129259</v>
       </c>
       <c r="F20">
-        <v>-3.396648614462837</v>
+        <v>0.3364586691149702</v>
       </c>
       <c r="G20">
-        <v>-11.46701105721315</v>
+        <v>-4.437948055255683</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-17.15031547287812</v>
       </c>
       <c r="E21">
-        <v>-33.58491283407562</v>
+        <v>-25.8631460490373</v>
       </c>
       <c r="F21">
-        <v>-2.632020769839142</v>
+        <v>0.5347433175882823</v>
       </c>
       <c r="G21">
-        <v>-10.73385653964754</v>
+        <v>-4.63499661401455</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-16.88768821854435</v>
       </c>
       <c r="E22">
-        <v>-33.96445820420641</v>
+        <v>-26.28554840682899</v>
       </c>
       <c r="F22">
-        <v>-2.822094640615906</v>
+        <v>0.9280024583933196</v>
       </c>
       <c r="G22">
-        <v>-11.03894945793733</v>
+        <v>-5.162625485133954</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-16.61117456226735</v>
       </c>
       <c r="E23">
-        <v>-35.22587154778333</v>
+        <v>-26.55589754480738</v>
       </c>
       <c r="F23">
-        <v>-3.189397717221623</v>
+        <v>1.072955156739594</v>
       </c>
       <c r="G23">
-        <v>-11.05851176715854</v>
+        <v>-4.519150044273079</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-16.32591645746623</v>
       </c>
       <c r="E24">
-        <v>-34.95261723848323</v>
+        <v>-26.82868046462212</v>
       </c>
       <c r="F24">
-        <v>-2.467405114452616</v>
+        <v>0.8824571618525971</v>
       </c>
       <c r="G24">
-        <v>-10.89055212463386</v>
+        <v>-5.046040074673199</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-16.02679076935338</v>
       </c>
       <c r="E25">
-        <v>-35.31936241131088</v>
+        <v>-25.89559508911819</v>
       </c>
       <c r="F25">
-        <v>-2.755904771662614</v>
+        <v>1.120954077527408</v>
       </c>
       <c r="G25">
-        <v>-11.21932841248194</v>
+        <v>-5.449590698355352</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-15.72629214619068</v>
       </c>
       <c r="E26">
-        <v>-34.46133179426359</v>
+        <v>-27.50637656933969</v>
       </c>
       <c r="F26">
-        <v>-2.977530328444607</v>
+        <v>1.042675014697661</v>
       </c>
       <c r="G26">
-        <v>-11.7219998706826</v>
+        <v>-5.435213327892091</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-15.43458953556437</v>
       </c>
       <c r="E27">
-        <v>-35.10775006449389</v>
+        <v>-26.75668869951754</v>
       </c>
       <c r="F27">
-        <v>-2.758725362669146</v>
+        <v>0.9988858570508733</v>
       </c>
       <c r="G27">
-        <v>-11.36166620758944</v>
+        <v>-5.20980163989537</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-15.16764848917918</v>
       </c>
       <c r="E28">
-        <v>-35.11877061074431</v>
+        <v>-26.11402077911357</v>
       </c>
       <c r="F28">
-        <v>-3.152721750462675</v>
+        <v>0.8398973014315642</v>
       </c>
       <c r="G28">
-        <v>-10.98507152181053</v>
+        <v>-5.640652819766796</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-14.94674424252528</v>
       </c>
       <c r="E29">
-        <v>-34.68369472859492</v>
+        <v>-26.40908567768602</v>
       </c>
       <c r="F29">
-        <v>-2.526149617189546</v>
+        <v>0.8693457626010866</v>
       </c>
       <c r="G29">
-        <v>-11.22032571691575</v>
+        <v>-6.361427186481352</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-14.77908039299658</v>
       </c>
       <c r="E30">
-        <v>-34.01250255281202</v>
+        <v>-26.91614294191168</v>
       </c>
       <c r="F30">
-        <v>-2.681603529101109</v>
+        <v>0.9686057150089402</v>
       </c>
       <c r="G30">
-        <v>-11.47011914864887</v>
+        <v>-6.058489437851522</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-14.67972161809665</v>
       </c>
       <c r="E31">
-        <v>-33.7396469517991</v>
+        <v>-26.37049819126704</v>
       </c>
       <c r="F31">
-        <v>-2.912441359769636</v>
+        <v>0.7735798638982414</v>
       </c>
       <c r="G31">
-        <v>-11.50951267378418</v>
+        <v>-6.260456639420045</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-14.64440987787119</v>
       </c>
       <c r="E32">
-        <v>-33.57499288882627</v>
+        <v>-25.33058391406587</v>
       </c>
       <c r="F32">
-        <v>-2.977117801478014</v>
+        <v>0.9173894152286524</v>
       </c>
       <c r="G32">
-        <v>-12.40828760672084</v>
+        <v>-6.49603195610997</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-14.67116138778678</v>
       </c>
       <c r="E33">
-        <v>-32.89848667915327</v>
+        <v>-25.36047872918198</v>
       </c>
       <c r="F33">
-        <v>-2.116286680162795</v>
+        <v>1.027457905508234</v>
       </c>
       <c r="G33">
-        <v>-11.47610689136859</v>
+        <v>-6.666902578853744</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-14.75283672045718</v>
       </c>
       <c r="E34">
-        <v>-33.2087564843859</v>
+        <v>-24.85960144340766</v>
       </c>
       <c r="F34">
-        <v>-2.154128159857482</v>
+        <v>1.341669258533726</v>
       </c>
       <c r="G34">
-        <v>-12.11715303438744</v>
+        <v>-6.973411826084218</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-14.87593313081765</v>
       </c>
       <c r="E35">
-        <v>-33.67806936409153</v>
+        <v>-24.00962182651355</v>
       </c>
       <c r="F35">
-        <v>-2.709023318501176</v>
+        <v>1.038070948672901</v>
       </c>
       <c r="G35">
-        <v>-12.47289570311712</v>
+        <v>-7.293964268470289</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-15.03558487794646</v>
       </c>
       <c r="E36">
-        <v>-31.96704597533397</v>
+        <v>-23.68600360008291</v>
       </c>
       <c r="F36">
-        <v>-2.694139213007674</v>
+        <v>1.478586793072845</v>
       </c>
       <c r="G36">
-        <v>-11.51536335241287</v>
+        <v>-7.121247849300598</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-15.21521362576344</v>
       </c>
       <c r="E37">
-        <v>-33.23361553077066</v>
+        <v>-23.0806481302212</v>
       </c>
       <c r="F37">
-        <v>-2.422370920599421</v>
+        <v>1.450669154863696</v>
       </c>
       <c r="G37">
-        <v>-12.1834685577463</v>
+        <v>-7.585386022708718</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-15.41229126168724</v>
       </c>
       <c r="E38">
-        <v>-32.15532558092808</v>
+        <v>-22.84346238467157</v>
       </c>
       <c r="F38">
-        <v>-2.305698685384721</v>
+        <v>1.520382898748496</v>
       </c>
       <c r="G38">
-        <v>-12.77486747624824</v>
+        <v>-7.474173524616474</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-15.61668539404106</v>
       </c>
       <c r="E39">
-        <v>-31.47489873976443</v>
+        <v>-22.04351235139634</v>
       </c>
       <c r="F39">
-        <v>-2.10059657318637</v>
+        <v>1.33475239072035</v>
       </c>
       <c r="G39">
-        <v>-12.29755287488877</v>
+        <v>-7.685258751669461</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-15.82276772587266</v>
       </c>
       <c r="E40">
-        <v>-30.26399052250309</v>
+        <v>-21.21941139426724</v>
       </c>
       <c r="F40">
-        <v>-2.779889321443271</v>
+        <v>1.683624292613778</v>
       </c>
       <c r="G40">
-        <v>-12.16147956142765</v>
+        <v>-7.94451743791767</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-16.03290923327267</v>
       </c>
       <c r="E41">
-        <v>-31.36058782786552</v>
+        <v>-21.16009523012604</v>
       </c>
       <c r="F41">
-        <v>-2.811686204199729</v>
+        <v>1.548524196156401</v>
       </c>
       <c r="G41">
-        <v>-13.74777450184956</v>
+        <v>-8.236790294892803</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-16.24059165074056</v>
       </c>
       <c r="E42">
-        <v>-30.22106708346098</v>
+        <v>-19.73102505178844</v>
       </c>
       <c r="F42">
-        <v>-2.472020777621015</v>
+        <v>1.477803157509796</v>
       </c>
       <c r="G42">
-        <v>-12.11344708244035</v>
+        <v>-8.468330705817163</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-16.45374583578028</v>
       </c>
       <c r="E43">
-        <v>-29.65303444716985</v>
+        <v>-19.23256493500516</v>
       </c>
       <c r="F43">
-        <v>-2.688969372046802</v>
+        <v>1.471996302016172</v>
       </c>
       <c r="G43">
-        <v>-13.4343598351756</v>
+        <v>-8.498517440151909</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-16.66742232647763</v>
       </c>
       <c r="E44">
-        <v>-28.73323104148272</v>
+        <v>-19.27442099873678</v>
       </c>
       <c r="F44">
-        <v>-2.177001040583582</v>
+        <v>1.054401383651691</v>
       </c>
       <c r="G44">
-        <v>-12.81786382891929</v>
+        <v>-8.570100140723349</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-16.88890491556016</v>
       </c>
       <c r="E45">
-        <v>-28.46656787855511</v>
+        <v>-18.85655810092313</v>
       </c>
       <c r="F45">
-        <v>-3.431167512504895</v>
+        <v>1.170427492292206</v>
       </c>
       <c r="G45">
-        <v>-12.63718072262981</v>
+        <v>-8.496471921764773</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-17.11840166646291</v>
       </c>
       <c r="E46">
-        <v>-28.25931225041786</v>
+        <v>-18.50043684266439</v>
       </c>
       <c r="F46">
-        <v>-2.194512727478763</v>
+        <v>1.175089544035162</v>
       </c>
       <c r="G46">
-        <v>-13.00887765155579</v>
+        <v>-8.483518712475965</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-17.35431103009937</v>
       </c>
       <c r="E47">
-        <v>-27.98248825598406</v>
+        <v>-17.93766424851615</v>
       </c>
       <c r="F47">
-        <v>-2.984642690965044</v>
+        <v>1.378523324284276</v>
       </c>
       <c r="G47">
-        <v>-14.01669816457407</v>
+        <v>-8.248440742630645</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-17.60327471549229</v>
       </c>
       <c r="E48">
-        <v>-27.36746826336948</v>
+        <v>-16.95002644226059</v>
       </c>
       <c r="F48">
-        <v>-2.681759262172835</v>
+        <v>1.321235091441467</v>
       </c>
       <c r="G48">
-        <v>-12.06743662513886</v>
+        <v>-9.051330858969488</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-17.85615534095296</v>
       </c>
       <c r="E49">
-        <v>-25.9940386571506</v>
+        <v>-15.95395346380431</v>
       </c>
       <c r="F49">
-        <v>-2.960935644264325</v>
+        <v>1.118903039838077</v>
       </c>
       <c r="G49">
-        <v>-12.78956335755162</v>
+        <v>-8.221359488987028</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-18.11775082031829</v>
       </c>
       <c r="E50">
-        <v>-26.90795280917912</v>
+        <v>-16.47870756148508</v>
       </c>
       <c r="F50">
-        <v>-3.005105022548997</v>
+        <v>1.129148287875901</v>
       </c>
       <c r="G50">
-        <v>-12.57067853103268</v>
+        <v>-8.396295041059165</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-18.37689762488366</v>
       </c>
       <c r="E51">
-        <v>-25.92444329498045</v>
+        <v>-15.22329560827253</v>
       </c>
       <c r="F51">
-        <v>-3.088997931267517</v>
+        <v>0.9248911104284047</v>
       </c>
       <c r="G51">
-        <v>-13.05920758578328</v>
+        <v>-8.605496615889663</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-18.63342502060997</v>
       </c>
       <c r="E52">
-        <v>-25.97326014089249</v>
+        <v>-14.81063668424889</v>
       </c>
       <c r="F52">
-        <v>-3.047254012738242</v>
+        <v>1.202513475272242</v>
       </c>
       <c r="G52">
-        <v>-13.20239387288288</v>
+        <v>-8.806629684561326</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-18.87993689489182</v>
       </c>
       <c r="E53">
-        <v>-25.82112801006402</v>
+        <v>-14.54048274720277</v>
       </c>
       <c r="F53">
-        <v>-3.157206531581431</v>
+        <v>0.5985441749519003</v>
       </c>
       <c r="G53">
-        <v>-12.6996427869722</v>
+        <v>-9.081561975962284</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-19.11003274848343</v>
       </c>
       <c r="E54">
-        <v>-25.32470296682991</v>
+        <v>-14.21055163955839</v>
       </c>
       <c r="F54">
-        <v>-3.549120403724322</v>
+        <v>1.012855444931684</v>
       </c>
       <c r="G54">
-        <v>-11.7069280421581</v>
+        <v>-8.492812963220327</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-19.32869248494269</v>
       </c>
       <c r="E55">
-        <v>-25.12580152327255</v>
+        <v>-14.18155807129976</v>
       </c>
       <c r="F55">
-        <v>-2.42019894126928</v>
+        <v>0.5184062556702704</v>
       </c>
       <c r="G55">
-        <v>-12.90983905549191</v>
+        <v>-9.525653547027542</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-19.5276525279712</v>
       </c>
       <c r="E56">
-        <v>-22.65964540464598</v>
+        <v>-13.77034446481716</v>
       </c>
       <c r="F56">
-        <v>-2.915628917535609</v>
+        <v>0.9164649572071281</v>
       </c>
       <c r="G56">
-        <v>-13.3381460647593</v>
+        <v>-9.180370826502148</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-19.7158181704023</v>
       </c>
       <c r="E57">
-        <v>-24.37697336819463</v>
+        <v>-13.19551509819294</v>
       </c>
       <c r="F57">
-        <v>-3.135308639288426</v>
+        <v>0.5846085501346041</v>
       </c>
       <c r="G57">
-        <v>-12.76954416802696</v>
+        <v>-8.728261658797583</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-19.88762599949479</v>
       </c>
       <c r="E58">
-        <v>-24.09174327403938</v>
+        <v>-12.77369834319806</v>
       </c>
       <c r="F58">
-        <v>-3.157572669973469</v>
+        <v>0.6539685811384095</v>
       </c>
       <c r="G58">
-        <v>-12.65691403562174</v>
+        <v>-9.264757923920703</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-20.04974516454673</v>
       </c>
       <c r="E59">
-        <v>-23.56610038913511</v>
+        <v>-12.4412794619701</v>
       </c>
       <c r="F59">
-        <v>-2.964355144903081</v>
+        <v>0.6429165032502585</v>
       </c>
       <c r="G59">
-        <v>-13.50895402963288</v>
+        <v>-9.294867641290013</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-20.20129546096448</v>
       </c>
       <c r="E60">
-        <v>-21.95158101872126</v>
+        <v>-11.77778318677212</v>
       </c>
       <c r="F60">
-        <v>-3.379354788194592</v>
+        <v>1.029295224407643</v>
       </c>
       <c r="G60">
-        <v>-13.85003475673888</v>
+        <v>-8.966519515554877</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-20.34234965263943</v>
       </c>
       <c r="E61">
-        <v>-23.50001033732311</v>
+        <v>-11.90590975614308</v>
       </c>
       <c r="F61">
-        <v>-2.965892594802677</v>
+        <v>0.8696390046616777</v>
       </c>
       <c r="G61">
-        <v>-14.39859527261753</v>
+        <v>-9.191779780365314</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-20.48140669363828</v>
       </c>
       <c r="E62">
-        <v>-22.85120812379237</v>
+        <v>-11.54109997979279</v>
       </c>
       <c r="F62">
-        <v>-3.016708793127413</v>
+        <v>0.7047011143554625</v>
       </c>
       <c r="G62">
-        <v>-13.04217378269856</v>
+        <v>-9.161719667143235</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-20.61126228186021</v>
       </c>
       <c r="E63">
-        <v>-23.33490772752721</v>
+        <v>-10.82800190174238</v>
       </c>
       <c r="F63">
-        <v>-3.417961679369466</v>
+        <v>0.8757374454810876</v>
       </c>
       <c r="G63">
-        <v>-13.26826687503356</v>
+        <v>-9.635556756707341</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-20.73919812780197</v>
       </c>
       <c r="E64">
-        <v>-23.97858903149443</v>
+        <v>-11.34506425204956</v>
       </c>
       <c r="F64">
-        <v>-3.333180760795144</v>
+        <v>0.9580572845016913</v>
       </c>
       <c r="G64">
-        <v>-14.28102952756281</v>
+        <v>-9.779497548993781</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-20.85448687972208</v>
       </c>
       <c r="E65">
-        <v>-23.61886278580573</v>
+        <v>-10.88833560265816</v>
       </c>
       <c r="F65">
-        <v>-2.667261175889039</v>
+        <v>0.8273210275222621</v>
       </c>
       <c r="G65">
-        <v>-14.01603895156482</v>
+        <v>-9.71153464579792</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-20.95700558743713</v>
       </c>
       <c r="E66">
-        <v>-22.34414255314406</v>
+        <v>-10.8741067006593</v>
       </c>
       <c r="F66">
-        <v>-3.167761589027903</v>
+        <v>0.4317838763595261</v>
       </c>
       <c r="G66">
-        <v>-14.33861080489211</v>
+        <v>-9.769226879772342</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-21.03843248821994</v>
       </c>
       <c r="E67">
-        <v>-21.34450196615975</v>
+        <v>-10.57227206762739</v>
       </c>
       <c r="F67">
-        <v>-2.665401491069754</v>
+        <v>0.4927633143492089</v>
       </c>
       <c r="G67">
-        <v>-13.5047194019061</v>
+        <v>-9.684714466613412</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-21.09295326465896</v>
       </c>
       <c r="E68">
-        <v>-23.08595178108301</v>
+        <v>-11.03836620855627</v>
       </c>
       <c r="F68">
-        <v>-3.794364371894936</v>
+        <v>0.4926357457691778</v>
       </c>
       <c r="G68">
-        <v>-13.72457803615752</v>
+        <v>-9.832660141102622</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-21.1225854309363</v>
       </c>
       <c r="E69">
-        <v>-23.0475096570604</v>
+        <v>-10.68560489825931</v>
       </c>
       <c r="F69">
-        <v>-3.627980980470835</v>
+        <v>0.5283582616475038</v>
       </c>
       <c r="G69">
-        <v>-14.5105061448879</v>
+        <v>-9.642629263804666</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-21.11655571885361</v>
       </c>
       <c r="E70">
-        <v>-20.71322630441979</v>
+        <v>-10.88751326681585</v>
       </c>
       <c r="F70">
-        <v>-3.319530094364411</v>
+        <v>0.5980993416565968</v>
       </c>
       <c r="G70">
-        <v>-13.75968732941881</v>
+        <v>-9.812331578343917</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-21.08232850673462</v>
       </c>
       <c r="E71">
-        <v>-21.47912000483142</v>
+        <v>-11.36414410487582</v>
       </c>
       <c r="F71">
-        <v>-3.62733733899886</v>
+        <v>0.3322952945484999</v>
       </c>
       <c r="G71">
-        <v>-14.27249630886676</v>
+        <v>-9.270427155800306</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-21.01364167927552</v>
       </c>
       <c r="E72">
-        <v>-22.55576112977804</v>
+        <v>-11.28650397236948</v>
       </c>
       <c r="F72">
-        <v>-3.38328373478607</v>
+        <v>0.6403336536883297</v>
       </c>
       <c r="G72">
-        <v>-13.47052125850711</v>
+        <v>-9.378376223153658</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-20.91848695830132</v>
       </c>
       <c r="E73">
-        <v>-23.33347486962014</v>
+        <v>-10.30467650875736</v>
       </c>
       <c r="F73">
-        <v>-3.610043512730615</v>
+        <v>0.3605873548237142</v>
       </c>
       <c r="G73">
-        <v>-13.2389051359896</v>
+        <v>-9.84065424104061</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-20.7989590103986</v>
       </c>
       <c r="E74">
-        <v>-23.1036652273834</v>
+        <v>-11.16876873773324</v>
       </c>
       <c r="F74">
-        <v>-3.515636964935763</v>
+        <v>0.1470292681775849</v>
       </c>
       <c r="G74">
-        <v>-13.36735376987238</v>
+        <v>-9.359290374820324</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-20.6585504914062</v>
       </c>
       <c r="E75">
-        <v>-23.49949118590751</v>
+        <v>-11.41503340323895</v>
       </c>
       <c r="F75">
-        <v>-3.84844102431709</v>
+        <v>0.1425279197107724</v>
       </c>
       <c r="G75">
-        <v>-13.23009517836689</v>
+        <v>-9.224497631581146</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-20.50727303624133</v>
       </c>
       <c r="E76">
-        <v>-22.61380641125385</v>
+        <v>-11.22041392055748</v>
       </c>
       <c r="F76">
-        <v>-3.572955847372475</v>
+        <v>0.195480477567328</v>
       </c>
       <c r="G76">
-        <v>-13.79424575557138</v>
+        <v>-9.439069508035564</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-20.34088216447181</v>
       </c>
       <c r="E77">
-        <v>-22.51610211483726</v>
+        <v>-11.87504724278828</v>
       </c>
       <c r="F77">
-        <v>-3.567502704759846</v>
+        <v>0.08731226210976854</v>
       </c>
       <c r="G77">
-        <v>-14.36145873618124</v>
+        <v>-9.117925731999605</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-20.1701932405933</v>
       </c>
       <c r="E78">
-        <v>-22.97564248829556</v>
+        <v>-11.70525981061797</v>
       </c>
       <c r="F78">
-        <v>-4.308797096381484</v>
+        <v>0.5178843842065067</v>
       </c>
       <c r="G78">
-        <v>-13.04451823134138</v>
+        <v>-8.853636140924321</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-19.9885270067189</v>
       </c>
       <c r="E79">
-        <v>-23.74479230638586</v>
+        <v>-11.67242452188387</v>
       </c>
       <c r="F79">
-        <v>-3.713659020942388</v>
+        <v>-0.1584287265025244</v>
       </c>
       <c r="G79">
-        <v>-13.56739815804955</v>
+        <v>-9.096484992045088</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-19.80020664814698</v>
       </c>
       <c r="E80">
-        <v>-22.76659474947164</v>
+        <v>-12.0120159990698</v>
       </c>
       <c r="F80">
-        <v>-3.689813636885402</v>
+        <v>0.1249217989316717</v>
       </c>
       <c r="G80">
-        <v>-13.46359625847918</v>
+        <v>-8.587328444280105</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-19.60316176940515</v>
       </c>
       <c r="E81">
-        <v>-24.5702389039842</v>
+        <v>-12.97171515274323</v>
       </c>
       <c r="F81">
-        <v>-3.97787260263711</v>
+        <v>0.08296830344948793</v>
       </c>
       <c r="G81">
-        <v>-12.78368918222161</v>
+        <v>-8.242560040439162</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-19.39537581931243</v>
       </c>
       <c r="E82">
-        <v>-24.5007016867726</v>
+        <v>-13.3847810914767</v>
       </c>
       <c r="F82">
-        <v>-4.301023696673614</v>
+        <v>0.2265425984375039</v>
       </c>
       <c r="G82">
-        <v>-12.70987821114166</v>
+        <v>-7.994658093162297</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-19.18287147936233</v>
       </c>
       <c r="E83">
-        <v>-25.29586722060163</v>
+        <v>-14.9853249057825</v>
       </c>
       <c r="F83">
-        <v>-3.947577549981927</v>
+        <v>-0.05478836726866705</v>
       </c>
       <c r="G83">
-        <v>-13.15303644101559</v>
+        <v>-8.164284696108405</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-18.95962091820528</v>
       </c>
       <c r="E84">
-        <v>-25.98993113115035</v>
+        <v>-14.78678063839907</v>
       </c>
       <c r="F84">
-        <v>-3.760794782896486</v>
+        <v>-0.2517600534085419</v>
       </c>
       <c r="G84">
-        <v>-13.21018302937047</v>
+        <v>-8.38034730772435</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-18.73794561470647</v>
       </c>
       <c r="E85">
-        <v>-27.51000232282627</v>
+        <v>-17.04189132355448</v>
       </c>
       <c r="F85">
-        <v>-3.695505349310037</v>
+        <v>-0.2347503571594569</v>
       </c>
       <c r="G85">
-        <v>-12.31961627742827</v>
+        <v>-8.002072607801058</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-18.51645540166637</v>
       </c>
       <c r="E86">
-        <v>-27.27199839464564</v>
+        <v>-16.05775882765708</v>
       </c>
       <c r="F86">
-        <v>-4.790486942537577</v>
+        <v>-0.2771959028789035</v>
       </c>
       <c r="G86">
-        <v>-13.25766464124905</v>
+        <v>-8.028779219595851</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-18.3043020488205</v>
       </c>
       <c r="E87">
-        <v>-28.65242200873553</v>
+        <v>-17.99629928600007</v>
       </c>
       <c r="F87">
-        <v>-3.693359877736786</v>
+        <v>-0.2346062212313697</v>
       </c>
       <c r="G87">
-        <v>-13.02426276943122</v>
+        <v>-7.203052920318542</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-18.10817653930177</v>
       </c>
       <c r="E88">
-        <v>-28.72016919186613</v>
+        <v>-18.18868849420011</v>
       </c>
       <c r="F88">
-        <v>-4.32202529543679</v>
+        <v>-0.1725084872479076</v>
       </c>
       <c r="G88">
-        <v>-13.12234061148558</v>
+        <v>-7.732819991258068</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-17.93016988693359</v>
       </c>
       <c r="E89">
-        <v>-29.87090983666469</v>
+        <v>-20.31281520059307</v>
       </c>
       <c r="F89">
-        <v>-4.190859115775308</v>
+        <v>-0.6021180464225928</v>
       </c>
       <c r="G89">
-        <v>-11.59889412560554</v>
+        <v>-7.452238048561941</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-17.78138282840046</v>
       </c>
       <c r="E90">
-        <v>-31.73314541994227</v>
+        <v>-21.73335052965815</v>
       </c>
       <c r="F90">
-        <v>-4.374068305885071</v>
+        <v>-0.4498939390145444</v>
       </c>
       <c r="G90">
-        <v>-12.13648168196774</v>
+        <v>-7.472949085403243</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-17.65746412316449</v>
       </c>
       <c r="E91">
-        <v>-32.68137755714785</v>
+        <v>-23.84311958450117</v>
       </c>
       <c r="F91">
-        <v>-4.404394008134159</v>
+        <v>-0.7202076182634819</v>
       </c>
       <c r="G91">
-        <v>-13.4988125922687</v>
+        <v>-7.416927727967133</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-17.56792214685942</v>
       </c>
       <c r="E92">
-        <v>-33.85684226896311</v>
+        <v>-25.38985023967117</v>
       </c>
       <c r="F92">
-        <v>-4.428138331368004</v>
+        <v>-0.765873856445013</v>
       </c>
       <c r="G92">
-        <v>-12.18728285559392</v>
+        <v>-7.492305145801756</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-17.50786125050296</v>
       </c>
       <c r="E93">
-        <v>-35.52067894725364</v>
+        <v>-27.17225071825724</v>
       </c>
       <c r="F93">
-        <v>-4.2099720368601</v>
+        <v>-0.8289863404969046</v>
       </c>
       <c r="G93">
-        <v>-13.26646676663799</v>
+        <v>-7.004508404908967</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-17.47838082170339</v>
       </c>
       <c r="E94">
-        <v>-36.55534979515721</v>
+        <v>-28.84197042038938</v>
       </c>
       <c r="F94">
-        <v>-4.16930085411745</v>
+        <v>-0.7279735626647272</v>
       </c>
       <c r="G94">
-        <v>-13.19514905664254</v>
+        <v>-7.366221846518531</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-17.48274105813095</v>
       </c>
       <c r="E95">
-        <v>-37.0322775878269</v>
+        <v>-31.35432686179334</v>
       </c>
       <c r="F95">
-        <v>-4.580914131466317</v>
+        <v>-1.12550707926821</v>
       </c>
       <c r="G95">
-        <v>-12.53728580234005</v>
+        <v>-7.396707511108961</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-17.51434279991566</v>
       </c>
       <c r="E96">
-        <v>-39.78659181459273</v>
+        <v>-32.88676839340026</v>
       </c>
       <c r="F96">
-        <v>-4.138714216136481</v>
+        <v>-1.346872528685725</v>
       </c>
       <c r="G96">
-        <v>-13.18771104530246</v>
+        <v>-7.930792753602188</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-17.57453504011144</v>
       </c>
       <c r="E97">
-        <v>-41.88618965490124</v>
+        <v>-35.4102035260132</v>
       </c>
       <c r="F97">
-        <v>-4.986749546180656</v>
+        <v>-1.478645073286056</v>
       </c>
       <c r="G97">
-        <v>-13.41171554196457</v>
+        <v>-7.379541865422391</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-17.65039268444606</v>
       </c>
       <c r="E98">
-        <v>-43.21600431239244</v>
+        <v>-38.34952670445482</v>
       </c>
       <c r="F98">
-        <v>-4.015633730693725</v>
+        <v>-1.501318317468081</v>
       </c>
       <c r="G98">
-        <v>-13.86675657584496</v>
+        <v>-8.448254079911502</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-17.73534221633998</v>
       </c>
       <c r="E99">
-        <v>-45.99712647995719</v>
+        <v>-40.52138419199838</v>
       </c>
       <c r="F99">
-        <v>-4.624587317676712</v>
+        <v>-1.754311662691884</v>
       </c>
       <c r="G99">
-        <v>-13.91408937528184</v>
+        <v>-8.363565441492673</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-17.8174899312072</v>
       </c>
       <c r="E100">
-        <v>-46.3994304098452</v>
+        <v>-42.63700927480942</v>
       </c>
       <c r="F100">
-        <v>-4.524706089716759</v>
+        <v>-2.002297526965763</v>
       </c>
       <c r="G100">
-        <v>-13.62889685763781</v>
+        <v>-9.145367268396797</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-17.87818001027988</v>
       </c>
       <c r="E101">
-        <v>-47.60497579298336</v>
+        <v>-44.48443865971398</v>
       </c>
       <c r="F101">
-        <v>-4.41017932607531</v>
+        <v>-2.165564600220532</v>
       </c>
       <c r="G101">
-        <v>-14.32292414601641</v>
+        <v>-8.882638902586999</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-17.92445369338053</v>
       </c>
       <c r="E102">
-        <v>-50.22996628721383</v>
+        <v>-46.65688590326566</v>
       </c>
       <c r="F102">
-        <v>-4.978035949470608</v>
+        <v>-2.331323402622921</v>
       </c>
       <c r="G102">
-        <v>-13.8895431546362</v>
+        <v>-8.686746903681996</v>
       </c>
     </row>
   </sheetData>
